--- a/pensum/ma04/MA04_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma04/MA04_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="151">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 4: Markedsundersøkelser (V5)</t>
   </si>
@@ -155,15 +155,42 @@
     <t xml:space="preserve">b)  Hva ble svarprosenten for SMS-skjemaet? Antall svar delt på antall spurt, ganger 100, med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Svarprosent = antall svar / antall spurt × 100. Skriftlige skjemaer gir ofte lav svarprosent (Markedsføring 4.3.1). Boka bruker begrepet svarprosent, men skriver ikke formelen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hva ble svarprosenten for telefonrunden? Antall svar delt på antall ringt, ganger 100, med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Svarprosent = antall svar / antall spurt × 100. Telefonintervju gir høy svarprosent og lav kostnad per intervju, og passer ved få spørsmål (Markedsføring 4.3.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Ronny foreslår at montøren selv spør kunden om han er fornøyd, ansikt til ansikt, før han går. Hva er det største problemet med det, ifølge boka?   A: Svarprosenten blir for lav   B: Kunden er ikke anonym og svarer lett det han tror montøren vil høre   C: Det blir sekundærdata, ikke primærdata   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Av dem som svarte, var 17 av 18 fornøyde på SMS (94,4 %) og 24 av 31 på telefon (77,4 %). Hvilken metode bør Tom bruke videre, og hvorfor? Skriv to setninger og ett tiltak.</t>
   </si>
   <si>
+    <t xml:space="preserve">Svarprosent og intervjuformene (Markedsføring 4.3.1), måleinstrument (4.4) og gyldighet: i hvilken grad svarene er representative for populasjonen (4.7.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problemstillingen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hvert forslag: hva skal måles, og hva skal svaret brukes til? Står det ikke, blir svaret like vagt som spørsmålet (4.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Svarprosenten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antall svar delt på antall spurt, ganger 100: 18 av 105 og 31 av 40. Del på dem som ble spurt, ikke på alle kundene i året.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 4, innledningen, avsnitt 4.1 (problemformulering) og 4.3.1 (intervjuformene). Nordlys Elektro AS er en konstruert casebedrift; undersøkelsene og svartallene er konstruerte.</t>
   </si>
   <si>
@@ -257,12 +284,30 @@
     <t xml:space="preserve">c)  Hva ble svarprosenten på skjemaet i postkassene? Antall svar delt på antall skjemaer, ganger 100.</t>
   </si>
   <si>
+    <t xml:space="preserve">Svarprosent = antall svar / antall spurt × 100. Skriftlige skjemaer gir ofte lav svarprosent (Markedsføring 4.3.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Styrelederen vil hoppe over undersøkelsen og regner 32,5 % av 48 plasser = 16 ladepunkter. Hva er svakheten i det?   A: Elbilforeningens tall er feil   B: Tallet er sekundærdata for hele landet og sier lite om akkurat dette borettslaget; det bør brukes sammen med primærdata   C: Ingen svakhet: offentlige tall er alltid bedre enn egne   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  25 av de 42 husstandene som svarte, har elbil eller planlegger det innen to år. Hva bør styret bygge beslutningen på, og hva vet de ikke ennå? To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Primær- og sekundærdata (Markedsføring 4.2), svarprosent (4.3.1) og gyldighet: om svarene er representative for populasjonen (4.7.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primær eller sekundær?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hver kilde: ble dataene samlet inn til akkurat dette spørsmålet, eller fantes de fra før? Telling og møte er primærdata, selv om ingen fyller ut et skjema (4.2–4.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snarveien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landstallet gjelder alle personbiler i Norge. Sammenlikn med hva beboerne selv svarte: 14 + 11 av 42.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 4, avsnitt 4.1 (problemformulering), 4.2 (primær- og sekundærdata) og 4.3 (innsamlingsmetoder). Elbilandelen: Elbilforeningen, årsberetning 2025. Fjell Elektro AS og borettslaget Haugtun er konstruerte; svartallene er konstruerte.</t>
   </si>
   <si>
@@ -305,15 +350,36 @@
     <t xml:space="preserve">b)  Hva ble svarprosenten? Antall svar delt på antall leiligheter som fikk skjema, ganger 100, med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Svarprosent = antall svar / antall spurt × 100. Gyldigheten bestemmes først og fremst av utvalgets størrelse og sammensetning (Markedsføring 4.7.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor stor andel av dem som svarte, vil ha ladepunkt de neste to årene? Del på antall svar, ikke antall spurt, og svar med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel = antall i kategorien / antall svar × 100. Frekvensfordelingen viser hvordan svarene fordeler seg på svaralternativene (Markedsføring 4.7.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Ida skriver i rapporten: «30,2 % av alle husstandene i de 22 borettslagene vil ha ladepunkt.» Hvilken vurdering er riktig?   A: Ja, 192 svar er nok til å si det sikkert   B: Nei, ikke uten videre: tallet gjelder dem som svarte, og gyldigheten avhenger av om svarerne og de fire borettslagene er representative   C: Nei, fordi klyngeutvalg ikke er et sannsynlighetsutvalg   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Bruk krysstabellen: hvor stor andel av dem med elbil og dem uten vil ha ladepunkt? Hva betyr det for Nordlys, og hva bør Kari gjøre før hun bestemmer seg? To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Krysstabell: viser hvordan to variabler virker sammen (Markedsføring 4.7.2). Gyldighet (4.7.3), tidsserieanalyse (4.9.2) og krav til rapporten (4.8).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utvalgsmetoden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trakk Kari husstander, eller trakk hun grupper av husstander og spurte alle i gruppa? Det siste har et eget navn (4.6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andelene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Svarprosent: 192 av 320. Andel som vil ha ladepunkt: 58 av 192, ikke av 320. I e) regner du 38 av 46 og 20 av 146.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 4, avsnitt 4.5 (populasjon og utvalg), 4.6 (utvalgsmetoder) og 4.7 (frekvensfordeling, krysstabell, gyldighet). Nordlys Elektro AS er en konstruert casebedrift; undersøkelsene og svartallene er konstruerte.</t>
   </si>
   <si>
@@ -377,9 +443,15 @@
     <t xml:space="preserve">a)  Hvor mange kunder må Mona ringe for å få 50 svar, når hun venter 75 % svar? Antall svar hun trenger delt på svarprosenten. Rund opp til helt tall.</t>
   </si>
   <si>
+    <t xml:space="preserve">Antall som må spørres = antall svar du trenger / svarprosent som desimaltall. Formelen står ikke i boka; den følger av svarprosenten. Telefonintervju gir høy svarprosent (Markedsføring 4.3.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange kunder måtte fått SMS-skjemaet for å gi 50 svar, med 15 % svar? Rund opp til helt tall.</t>
   </si>
   <si>
+    <t xml:space="preserve">Antall som må spørres = svar du trenger / svarprosent. Skriftlige skjemaer gir ofte lav svarprosent (Markedsføring 4.3.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvordan bør Mona velge ut de 67 kundene hun skal ringe, hvis svaret skal gjelde alle kundene?   A: Ringe de kundene hun husker best   B: Ringe de 67 første i kunderegisteret (januar og februar)   C: Nummerere alle 280 og la regnearket trekke 67 tilfeldig   (skriv bokstaven)</t>
   </si>
   <si>
@@ -387,6 +459,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Mona tenker å ringe kundene selv. Hva kan svekke påliteligheten i undersøkelsen, og hvordan kan hun unngå det? To–tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fravær av anonymitet (Markedsføring 4.3.1), måleinstrument (4.4), pålitelighet som resultat av gjennomføringen (4.7.3) og krav til rapporten (4.8).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fra svar til spurte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antall som må spørres = svar du trenger / svarprosent som desimaltall: 50 / 0,75 og 50 / 0,15. Rund alltid opp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trekking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Får alle 280 like stor sjanse? Det gjør de bare hvis alle får et nummer og numrene trekkes tilfeldig (4.6).</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 4, avsnitt 4.3.1 (intervjuformene), 4.5 (utvalget bør ikke være større enn nødvendig), 4.6 (utvalgsmetoder) og 4.7.3 (gyldighet og pålitelighet). Fjell Elektro AS og borettslaget Haugtun er konstruerte; svartallene er konstruerte.</t>
@@ -400,7 +487,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,8 +554,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -484,13 +593,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +670,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -624,7 +751,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -661,8 +808,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -676,7 +823,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -690,7 +837,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -993,7 +1140,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1161,33 +1308,18 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="19" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(77.5))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="B19" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="19" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
@@ -1197,70 +1329,167 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="F21" s="16"/>
+      <c r="G21" s="19" t="str">
+        <f aca="false">IF(F21="","",IF(ABS(F21-(77.5))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+    </row>
+    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1277,7 +1506,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1288,7 +1517,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1298,7 +1527,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1309,7 +1538,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1320,10 +1549,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -1332,11 +1561,11 @@
       <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>53</v>
+      <c r="A8" s="26" t="s">
+        <v>62</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1345,11 +1574,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>55</v>
+      <c r="A9" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1358,11 +1587,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>57</v>
+      <c r="A10" s="26" t="s">
+        <v>66</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1371,11 +1600,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="26" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1384,11 +1613,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>60</v>
+      <c r="A12" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1397,11 +1626,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>62</v>
+      <c r="A13" s="26" t="s">
+        <v>71</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1410,11 +1639,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>64</v>
+      <c r="A14" s="26" t="s">
+        <v>73</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1423,11 +1652,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
-        <v>66</v>
+      <c r="A15" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1452,7 +1681,7 @@
     </row>
     <row r="18" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1466,7 +1695,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1475,7 +1704,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1489,7 +1718,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1503,7 +1732,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1517,7 +1746,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1531,7 +1760,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1545,7 +1774,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1559,7 +1788,7 @@
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1571,80 +1800,143 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="19" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+    </row>
+    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="19" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="31">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1666,11 +1958,16 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1687,7 +1984,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1698,7 +1995,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1708,7 +2005,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1719,7 +2016,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1733,15 +2030,15 @@
         <v>24</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>22</v>
@@ -1750,7 +2047,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>4</v>
@@ -1759,7 +2056,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>320</v>
@@ -1768,7 +2065,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>46</v>
@@ -1779,7 +2076,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>146</v>
@@ -1790,7 +2087,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B13" s="14" t="n">
         <v>192</v>
@@ -1834,7 +2131,7 @@
     </row>
     <row r="18" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1848,7 +2145,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1860,106 +2157,188 @@
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="19" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(30.2))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="19" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="19" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(30.2))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+    </row>
+    <row r="25" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+    </row>
+    <row r="37" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1976,7 +2355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1987,7 +2366,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1997,7 +2376,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2008,7 +2387,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2019,10 +2398,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -2031,11 +2410,11 @@
       <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>100</v>
+      <c r="A8" s="26" t="s">
+        <v>122</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2044,11 +2423,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>102</v>
+      <c r="A9" s="26" t="s">
+        <v>124</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2057,11 +2436,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>104</v>
+      <c r="A10" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2070,11 +2449,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>106</v>
+      <c r="A11" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2083,11 +2462,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>108</v>
+      <c r="A12" s="26" t="s">
+        <v>130</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2096,11 +2475,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>110</v>
+      <c r="A13" s="26" t="s">
+        <v>132</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2109,11 +2488,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>112</v>
+      <c r="A14" s="26" t="s">
+        <v>134</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2122,11 +2501,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
-        <v>114</v>
+      <c r="A15" s="26" t="s">
+        <v>136</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2151,7 +2530,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2163,108 +2542,184 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="19" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(334))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="19" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="C","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="18"/>
+      <c r="F21" s="16"/>
       <c r="G21" s="19" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(334))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+    </row>
+    <row r="24" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="C","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+    </row>
+    <row r="37" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="26">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2278,13 +2733,19 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ma04/MA04_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma04/MA04_Klasseoppgaver_v5.xlsx
@@ -425,7 +425,7 @@
     <t xml:space="preserve">Monas timepris</t>
   </si>
   <si>
-    <t xml:space="preserve">890 kr uten mva (tapt fakturering per time)</t>
+    <t xml:space="preserve">890 kr uten merverdiavgift (tapt fakturering per time)</t>
   </si>
   <si>
     <t xml:space="preserve">Montørens forslag</t>

--- a/pensum/ma04/MA04_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma04/MA04_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="151">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 4: Markedsundersøkelser (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 4: Markedsundersøkelser (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ma04/MA04_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma04/MA04_Klasseoppgaver_v5.xlsx
@@ -452,7 +452,7 @@
     <t xml:space="preserve">Antall som må spørres = svar du trenger / svarprosent. Skriftlige skjemaer gir ofte lav svarprosent (Markedsføring 4.3.1).</t>
   </si>
   <si>
-    <t xml:space="preserve">c)  Hvordan bør Mona velge ut de 67 kundene hun skal ringe, hvis svaret skal gjelde alle kundene?   A: Ringe de kundene hun husker best   B: Ringe de 67 første i kunderegisteret (januar og februar)   C: Nummerere alle 280 og la regnearket trekke 67 tilfeldig   (skriv bokstaven)</t>
+    <t xml:space="preserve">c)  Hvordan bør Mona velge ut de 67 kundene hun skal ringe (50 / 0,75, svaret i a), hvis svaret skal gjelde alle kundene?   A: Ringe de kundene hun husker best   B: Ringe de 67 første i kunderegisteret (januar og februar)   C: Nummerere alle 280 og la regnearket trekke 67 tilfeldig   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Montøren mener Mona bør ringe alle 280, fordi flere svar alltid er bedre. Hva sier boka?   A: Han har rett: ring alltid alle   B: Utvalget bør ikke være større enn nødvendig; et godt trukket utvalg gir svaret billigere   C: Flere svar gir lavere gyldighet   (skriv bokstaven)</t>
@@ -2582,7 +2582,7 @@
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
     </row>
-    <row r="24" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
         <v>142</v>
       </c>
